--- a/output/yearly_benthic_cover_iteration_68_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_68_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.82069257582242</v>
+        <v>45.82091205479438</v>
       </c>
       <c r="M2" t="n">
-        <v>98.05857005079423</v>
+        <v>98.92042116581862</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.0491867474323</v>
+        <v>87.9649233419768</v>
       </c>
       <c r="C3" t="n">
-        <v>45.92167428108734</v>
+        <v>45.89465883410496</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228792039898368</v>
+        <v>2.228596300253429</v>
       </c>
       <c r="E3" t="n">
-        <v>5.703604327060186</v>
+        <v>5.683521350615565</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429306799661229</v>
+        <v>0.7428654334178099</v>
       </c>
       <c r="G3" t="n">
-        <v>33.97044882661412</v>
+        <v>33.96196144866307</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17481127844165</v>
+        <v>34.17180993721925</v>
       </c>
       <c r="I3" t="n">
-        <v>6.58528284566358</v>
+        <v>6.53325991294636</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643316749788268</v>
+        <v>4.642908958861311</v>
       </c>
       <c r="K3" t="n">
-        <v>11.95081325256771</v>
+        <v>12.03507665802322</v>
       </c>
       <c r="L3" t="n">
-        <v>48.89114109646285</v>
+        <v>48.83573984632757</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7636286301179</v>
+        <v>106.7654753384557</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.06654850502332</v>
+        <v>87.04766316789672</v>
       </c>
       <c r="C4" t="n">
-        <v>42.57776024858311</v>
+        <v>42.60708156900124</v>
       </c>
       <c r="D4" t="n">
-        <v>2.18110843907299</v>
+        <v>2.184332405713654</v>
       </c>
       <c r="E4" t="n">
-        <v>6.498127568811149</v>
+        <v>6.479929416752189</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444948440098358</v>
+        <v>0.7444174160026867</v>
       </c>
       <c r="G4" t="n">
-        <v>33.24367248646663</v>
+        <v>33.28741636404789</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24676282445244</v>
+        <v>34.24320113612359</v>
       </c>
       <c r="I4" t="n">
-        <v>5.499289567148798</v>
+        <v>5.455757579239909</v>
       </c>
       <c r="J4" t="n">
-        <v>4.653092775061474</v>
+        <v>4.652608850016792</v>
       </c>
       <c r="K4" t="n">
-        <v>12.93345149497668</v>
+        <v>12.95233683210329</v>
       </c>
       <c r="L4" t="n">
-        <v>44.30586373294958</v>
+        <v>44.2591021568692</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81707547650936</v>
+        <v>99.81852055797373</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.94659497673054</v>
+        <v>85.88214259982041</v>
       </c>
       <c r="C5" t="n">
-        <v>42.31124002772738</v>
+        <v>42.28831914266787</v>
       </c>
       <c r="D5" t="n">
-        <v>2.126620780923791</v>
+        <v>2.127400331374317</v>
       </c>
       <c r="E5" t="n">
-        <v>7.100943873071823</v>
+        <v>7.070121218344913</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7458204354492195</v>
+        <v>0.745733347425016</v>
       </c>
       <c r="G5" t="n">
-        <v>32.41319114513709</v>
+        <v>32.41981871359631</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30774003066409</v>
+        <v>34.30373398155074</v>
       </c>
       <c r="I5" t="n">
-        <v>4.590900989926892</v>
+        <v>4.554501586122768</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661377721557622</v>
+        <v>4.660833421406349</v>
       </c>
       <c r="K5" t="n">
-        <v>14.05340502326946</v>
+        <v>14.11785740017961</v>
       </c>
       <c r="L5" t="n">
-        <v>43.48259690547125</v>
+        <v>43.44227463550697</v>
       </c>
       <c r="M5" t="n">
-        <v>99.8472419564681</v>
+        <v>99.84845117835444</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.51730578357227</v>
+        <v>84.53809649076355</v>
       </c>
       <c r="C6" t="n">
-        <v>41.59491217891351</v>
+        <v>41.651597166423</v>
       </c>
       <c r="D6" t="n">
-        <v>2.056729364595764</v>
+        <v>2.061780736666761</v>
       </c>
       <c r="E6" t="n">
-        <v>7.506159951594391</v>
+        <v>7.485561301124349</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7469474767886696</v>
+        <v>0.7468510335985747</v>
       </c>
       <c r="G6" t="n">
-        <v>31.34793124682055</v>
+        <v>31.41983044946723</v>
       </c>
       <c r="H6" t="n">
-        <v>34.3595839322788</v>
+        <v>34.35514754553444</v>
       </c>
       <c r="I6" t="n">
-        <v>3.831532081564935</v>
+        <v>3.801106464381095</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668421729929185</v>
+        <v>4.667818959991092</v>
       </c>
       <c r="K6" t="n">
-        <v>15.48269421642772</v>
+        <v>15.46190350923645</v>
       </c>
       <c r="L6" t="n">
-        <v>42.79486857716079</v>
+        <v>42.75998539139272</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87247497250203</v>
+        <v>99.87348606705217</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.81252227106658</v>
+        <v>82.97279389475374</v>
       </c>
       <c r="C7" t="n">
-        <v>40.48514176084439</v>
+        <v>40.67665237823338</v>
       </c>
       <c r="D7" t="n">
-        <v>1.973560401619148</v>
+        <v>1.985529433156063</v>
       </c>
       <c r="E7" t="n">
-        <v>7.735471767861537</v>
+        <v>7.73732521760115</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7479086962076834</v>
+        <v>0.7478026431991167</v>
       </c>
       <c r="G7" t="n">
-        <v>30.08029974501003</v>
+        <v>30.25782375047642</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40380002555343</v>
+        <v>34.39892158715937</v>
       </c>
       <c r="I7" t="n">
-        <v>3.197052283516742</v>
+        <v>3.171624743167141</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674429351298021</v>
+        <v>4.673766519994479</v>
       </c>
       <c r="K7" t="n">
-        <v>17.1874777289334</v>
+        <v>17.02720610524625</v>
       </c>
       <c r="L7" t="n">
-        <v>42.22094906351209</v>
+        <v>42.19055522584311</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89356855328988</v>
+        <v>99.89441370932275</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.56611857892803</v>
+        <v>87.85591888953029</v>
       </c>
       <c r="C8" t="n">
-        <v>42.74399150591584</v>
+        <v>42.96391801606865</v>
       </c>
       <c r="D8" t="n">
-        <v>1.97774524541087</v>
+        <v>1.989780953383558</v>
       </c>
       <c r="E8" t="n">
-        <v>9.535627809773317</v>
+        <v>9.560911394204687</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7494946020971268</v>
+        <v>0.749403877615814</v>
       </c>
       <c r="G8" t="n">
-        <v>30.57176051085182</v>
+        <v>30.75581839562273</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47675169646783</v>
+        <v>34.47257837032745</v>
       </c>
       <c r="I8" t="n">
-        <v>5.570397451220037</v>
+        <v>5.643651663277211</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684341263107043</v>
+        <v>4.683774235098837</v>
       </c>
       <c r="K8" t="n">
-        <v>12.43388142107196</v>
+        <v>12.14408111046973</v>
       </c>
       <c r="L8" t="n">
-        <v>44.6368400505554</v>
+        <v>44.70428110680653</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81471297754319</v>
+        <v>99.81228023334489</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.4380306682978</v>
+        <v>85.77538503729259</v>
       </c>
       <c r="C9" t="n">
-        <v>41.48020657017233</v>
+        <v>41.75922127737763</v>
       </c>
       <c r="D9" t="n">
-        <v>1.881144923504713</v>
+        <v>1.895392375393954</v>
       </c>
       <c r="E9" t="n">
-        <v>9.844942829993474</v>
+        <v>9.892649341520585</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508544433387506</v>
+        <v>0.7507760397406954</v>
       </c>
       <c r="G9" t="n">
-        <v>29.0785237487163</v>
+        <v>29.29686485687622</v>
       </c>
       <c r="H9" t="n">
-        <v>34.53930439358253</v>
+        <v>34.535697828072</v>
       </c>
       <c r="I9" t="n">
-        <v>4.650420058294829</v>
+        <v>4.711654347309809</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692840270867191</v>
+        <v>4.692350248379347</v>
       </c>
       <c r="K9" t="n">
-        <v>14.56196933170221</v>
+        <v>14.22461496270739</v>
       </c>
       <c r="L9" t="n">
-        <v>43.80309083559157</v>
+        <v>43.8593956581573</v>
       </c>
       <c r="M9" t="n">
-        <v>99.8452667374661</v>
+        <v>99.84323189824232</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.18448939899287</v>
+        <v>83.52587153513933</v>
       </c>
       <c r="C10" t="n">
-        <v>39.94781635101148</v>
+        <v>40.24056554850455</v>
       </c>
       <c r="D10" t="n">
-        <v>1.780017995117205</v>
+        <v>1.794426085684283</v>
       </c>
       <c r="E10" t="n">
-        <v>9.962592864924991</v>
+        <v>10.02109793905078</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7520222690387532</v>
+        <v>0.7519543003346333</v>
       </c>
       <c r="G10" t="n">
-        <v>27.51531521969331</v>
+        <v>27.73624037451297</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59302437578265</v>
+        <v>34.58989781539314</v>
       </c>
       <c r="I10" t="n">
-        <v>3.881377492943757</v>
+        <v>3.93254064307208</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700139181492207</v>
+        <v>4.699714377091459</v>
       </c>
       <c r="K10" t="n">
-        <v>16.81551060100714</v>
+        <v>16.47412846486066</v>
       </c>
       <c r="L10" t="n">
-        <v>43.10749471302874</v>
+        <v>43.15442669920952</v>
       </c>
       <c r="M10" t="n">
-        <v>99.87082166504737</v>
+        <v>99.86912071257473</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>80.81859188544792</v>
+        <v>81.23321525121654</v>
       </c>
       <c r="C11" t="n">
-        <v>38.18313104258262</v>
+        <v>38.55724861608654</v>
       </c>
       <c r="D11" t="n">
-        <v>1.674978872906117</v>
+        <v>1.692686658702857</v>
       </c>
       <c r="E11" t="n">
-        <v>9.914499130957557</v>
+        <v>9.99984866136159</v>
       </c>
       <c r="F11" t="n">
-        <v>0.753026844491011</v>
+        <v>0.7529668420572246</v>
       </c>
       <c r="G11" t="n">
-        <v>25.89163244459435</v>
+        <v>26.16366559707602</v>
       </c>
       <c r="H11" t="n">
-        <v>34.6392348465865</v>
+        <v>34.63647473463234</v>
       </c>
       <c r="I11" t="n">
-        <v>3.238801967843556</v>
+        <v>3.281529994528857</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706417778068817</v>
+        <v>4.706042762857655</v>
       </c>
       <c r="K11" t="n">
-        <v>19.18140811455208</v>
+        <v>18.76678474878347</v>
       </c>
       <c r="L11" t="n">
-        <v>42.52764480139465</v>
+        <v>42.56672939504466</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89218395852936</v>
+        <v>99.89076275991467</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>78.40078764352116</v>
+        <v>78.93314943946869</v>
       </c>
       <c r="C12" t="n">
-        <v>36.26616665766723</v>
+        <v>36.76487000224552</v>
       </c>
       <c r="D12" t="n">
-        <v>1.568730707536711</v>
+        <v>1.591680563478078</v>
       </c>
       <c r="E12" t="n">
-        <v>9.735947656409712</v>
+        <v>9.859432112990467</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538919529839851</v>
+        <v>0.7538373888497653</v>
       </c>
       <c r="G12" t="n">
-        <v>24.24926041820324</v>
+        <v>24.60242584538287</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67902983726331</v>
+        <v>34.67651988708921</v>
       </c>
       <c r="I12" t="n">
-        <v>2.702102364974298</v>
+        <v>2.737769961367277</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711824706149906</v>
+        <v>4.711483680311034</v>
       </c>
       <c r="K12" t="n">
-        <v>21.59921235647883</v>
+        <v>21.06685056053131</v>
       </c>
       <c r="L12" t="n">
-        <v>42.04465426452495</v>
+        <v>42.07712582626404</v>
       </c>
       <c r="M12" t="n">
-        <v>99.91003327867101</v>
+        <v>99.90884638904087</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>75.98953099618521</v>
+        <v>76.65016809022124</v>
       </c>
       <c r="C13" t="n">
-        <v>34.27186608293301</v>
+        <v>34.90464038942142</v>
       </c>
       <c r="D13" t="n">
-        <v>1.463785746875862</v>
+        <v>1.492372874309599</v>
       </c>
       <c r="E13" t="n">
-        <v>9.460295199550488</v>
+        <v>9.624908645307578</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7546373434358248</v>
+        <v>0.7545860583117234</v>
       </c>
       <c r="G13" t="n">
-        <v>22.62703318161203</v>
+        <v>23.06743816336643</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71331779804794</v>
+        <v>34.71095868233929</v>
       </c>
       <c r="I13" t="n">
-        <v>2.253978330189159</v>
+        <v>2.283740802138353</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716483396473904</v>
+        <v>4.716162864448274</v>
       </c>
       <c r="K13" t="n">
-        <v>24.01046900381478</v>
+        <v>23.34983190977875</v>
       </c>
       <c r="L13" t="n">
-        <v>41.64260651422514</v>
+        <v>41.66947853520631</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92494160097294</v>
+        <v>99.92395083440647</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.04460846408095</v>
+        <v>83.50645203658979</v>
       </c>
       <c r="C14" t="n">
-        <v>38.79618081741271</v>
+        <v>39.25537494317864</v>
       </c>
       <c r="D14" t="n">
-        <v>1.465379066722852</v>
+        <v>1.494046454304713</v>
       </c>
       <c r="E14" t="n">
-        <v>11.94423482190067</v>
+        <v>12.0302718619275</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7554587605449492</v>
+        <v>0.7554322678304849</v>
       </c>
       <c r="G14" t="n">
-        <v>24.67333752115039</v>
+        <v>25.019646206026</v>
       </c>
       <c r="H14" t="n">
-        <v>36.77277796807368</v>
+        <v>36.67622402679568</v>
       </c>
       <c r="I14" t="n">
-        <v>2.711803072282479</v>
+        <v>2.809379545764878</v>
       </c>
       <c r="J14" t="n">
-        <v>4.721617253405932</v>
+        <v>4.721451673940533</v>
       </c>
       <c r="K14" t="n">
-        <v>16.95539153591904</v>
+        <v>16.49354796341022</v>
       </c>
       <c r="L14" t="n">
-        <v>44.15813249652167</v>
+        <v>44.15753600759773</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90970484985344</v>
+        <v>99.90645891418659</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.2869741257596</v>
+        <v>82.85631907188345</v>
       </c>
       <c r="C15" t="n">
-        <v>38.45479442663735</v>
+        <v>39.03022700054091</v>
       </c>
       <c r="D15" t="n">
-        <v>1.437426581785078</v>
+        <v>1.469156496829011</v>
       </c>
       <c r="E15" t="n">
-        <v>12.09380334180604</v>
+        <v>12.22965100986191</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7561517404486473</v>
+        <v>0.7561444433560087</v>
       </c>
       <c r="G15" t="n">
-        <v>24.20268722247582</v>
+        <v>24.61207037101325</v>
       </c>
       <c r="H15" t="n">
-        <v>36.80650951963666</v>
+        <v>36.72003726512371</v>
       </c>
       <c r="I15" t="n">
-        <v>2.264447341803324</v>
+        <v>2.343356714724492</v>
       </c>
       <c r="J15" t="n">
-        <v>4.725948377804045</v>
+        <v>4.725902770975057</v>
       </c>
       <c r="K15" t="n">
-        <v>17.7130258742404</v>
+        <v>17.14368092811655</v>
       </c>
       <c r="L15" t="n">
-        <v>43.75676729661765</v>
+        <v>43.74805375062687</v>
       </c>
       <c r="M15" t="n">
-        <v>99.92458759749539</v>
+        <v>99.92196167928432</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>79.84998179950776</v>
+        <v>80.46826686868832</v>
       </c>
       <c r="C16" t="n">
-        <v>36.36758313551418</v>
+        <v>37.00443632824344</v>
       </c>
       <c r="D16" t="n">
-        <v>1.345652423155863</v>
+        <v>1.378694056052954</v>
       </c>
       <c r="E16" t="n">
-        <v>11.63641503463576</v>
+        <v>11.8023471984361</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7567478637628836</v>
+        <v>0.7567566069196529</v>
       </c>
       <c r="G16" t="n">
-        <v>22.65743873148828</v>
+        <v>23.09659672125607</v>
       </c>
       <c r="H16" t="n">
-        <v>36.83552647121743</v>
+        <v>36.74976527419245</v>
       </c>
       <c r="I16" t="n">
-        <v>1.888527126729514</v>
+        <v>1.954378218583254</v>
       </c>
       <c r="J16" t="n">
-        <v>4.729674148518022</v>
+        <v>4.729728793247832</v>
       </c>
       <c r="K16" t="n">
-        <v>20.15001820049226</v>
+        <v>19.5317331313117</v>
       </c>
       <c r="L16" t="n">
-        <v>43.41949734894347</v>
+        <v>43.39873729836918</v>
       </c>
       <c r="M16" t="n">
-        <v>99.9370986849499</v>
+        <v>99.93490675792431</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>81.58942274693815</v>
+        <v>82.27876671495211</v>
       </c>
       <c r="C17" t="n">
-        <v>37.64319934685441</v>
+        <v>38.3205109787443</v>
       </c>
       <c r="D17" t="n">
-        <v>1.346670288387319</v>
+        <v>1.379774190738968</v>
       </c>
       <c r="E17" t="n">
-        <v>12.42344886665667</v>
+        <v>12.61630849687283</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7573202755731315</v>
+        <v>0.7573494861421426</v>
       </c>
       <c r="G17" t="n">
-        <v>23.1442336165455</v>
+        <v>23.597100921146</v>
       </c>
       <c r="H17" t="n">
-        <v>37.33304580659367</v>
+        <v>37.26096601757096</v>
       </c>
       <c r="I17" t="n">
-        <v>1.851452170849802</v>
+        <v>1.933833314092815</v>
       </c>
       <c r="J17" t="n">
-        <v>4.733251722332072</v>
+        <v>4.733434288388393</v>
       </c>
       <c r="K17" t="n">
-        <v>18.41057725306184</v>
+        <v>17.7212332850479</v>
       </c>
       <c r="L17" t="n">
-        <v>43.88455497434892</v>
+        <v>43.89384508811208</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93833157426518</v>
+        <v>99.93558935190428</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>79.20216575938346</v>
+        <v>79.94300239448513</v>
       </c>
       <c r="C18" t="n">
-        <v>35.54156219444815</v>
+        <v>36.28335673472364</v>
       </c>
       <c r="D18" t="n">
-        <v>1.260399338654485</v>
+        <v>1.294915273054345</v>
       </c>
       <c r="E18" t="n">
-        <v>11.88488595914559</v>
+        <v>12.1091484354784</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7578123543338139</v>
+        <v>0.7578587282869763</v>
       </c>
       <c r="G18" t="n">
-        <v>21.66155813750967</v>
+        <v>22.14583124375712</v>
       </c>
       <c r="H18" t="n">
-        <v>37.35730344171258</v>
+        <v>37.28602030835818</v>
       </c>
       <c r="I18" t="n">
-        <v>1.543879313440983</v>
+        <v>1.612611353756506</v>
       </c>
       <c r="J18" t="n">
-        <v>4.736327214586336</v>
+        <v>4.736617051793604</v>
       </c>
       <c r="K18" t="n">
-        <v>20.79783424061656</v>
+        <v>20.05699760551487</v>
       </c>
       <c r="L18" t="n">
-        <v>43.60917433796725</v>
+        <v>43.60592806770337</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94857077303195</v>
+        <v>99.94628240794187</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>78.22138998536384</v>
+        <v>79.01590858493375</v>
       </c>
       <c r="C19" t="n">
-        <v>34.78684415735305</v>
+        <v>35.59899489313587</v>
       </c>
       <c r="D19" t="n">
-        <v>1.22507961063412</v>
+        <v>1.261625218827049</v>
       </c>
       <c r="E19" t="n">
-        <v>11.76823627854315</v>
+        <v>12.02285432323159</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7582316457659209</v>
+        <v>0.758290354840946</v>
       </c>
       <c r="G19" t="n">
-        <v>21.05454390126696</v>
+        <v>21.57649984551491</v>
       </c>
       <c r="H19" t="n">
-        <v>37.37797293485314</v>
+        <v>37.30725597650615</v>
       </c>
       <c r="I19" t="n">
-        <v>1.29837782826354</v>
+        <v>1.350068148257179</v>
       </c>
       <c r="J19" t="n">
-        <v>4.738947786037006</v>
+        <v>4.739314717755915</v>
       </c>
       <c r="K19" t="n">
-        <v>21.77861001463616</v>
+        <v>20.98409141506626</v>
       </c>
       <c r="L19" t="n">
-        <v>43.39129049989106</v>
+        <v>43.37193703593831</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95674467188027</v>
+        <v>99.95502334414044</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>75.61541924425705</v>
+        <v>76.51566225409726</v>
       </c>
       <c r="C20" t="n">
-        <v>32.38045094902883</v>
+        <v>33.30653287661374</v>
       </c>
       <c r="D20" t="n">
-        <v>1.131853761106188</v>
+        <v>1.171715128490596</v>
       </c>
       <c r="E20" t="n">
-        <v>11.05311582567328</v>
+        <v>11.35364350466063</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7585934697282546</v>
+        <v>0.7586621907169834</v>
       </c>
       <c r="G20" t="n">
-        <v>19.45233966524775</v>
+        <v>20.03884427133552</v>
       </c>
       <c r="H20" t="n">
-        <v>37.39580949752737</v>
+        <v>37.32554999293404</v>
       </c>
       <c r="I20" t="n">
-        <v>1.082497839172602</v>
+        <v>1.125608473978339</v>
       </c>
       <c r="J20" t="n">
-        <v>4.741209185801591</v>
+        <v>4.741638691981148</v>
       </c>
       <c r="K20" t="n">
-        <v>24.38458075574298</v>
+        <v>23.48433774590274</v>
       </c>
       <c r="L20" t="n">
-        <v>43.19890224444309</v>
+        <v>43.17162748447638</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96393394921489</v>
+        <v>99.96249810699285</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>81.55941071961934</v>
+        <v>82.35776795271285</v>
       </c>
       <c r="C21" t="n">
-        <v>36.18482671091183</v>
+        <v>36.99757202903496</v>
       </c>
       <c r="D21" t="n">
-        <v>1.132508143823099</v>
+        <v>1.172442238491463</v>
       </c>
       <c r="E21" t="n">
-        <v>13.07294767629518</v>
+        <v>13.32695083422145</v>
       </c>
       <c r="F21" t="n">
-        <v>0.759032051524605</v>
+        <v>0.759132979949568</v>
       </c>
       <c r="G21" t="n">
-        <v>21.24125914366489</v>
+        <v>21.76200488846296</v>
       </c>
       <c r="H21" t="n">
-        <v>39.19510301625179</v>
+        <v>39.05943790742804</v>
       </c>
       <c r="I21" t="n">
-        <v>1.414610366030978</v>
+        <v>1.533217979474565</v>
       </c>
       <c r="J21" t="n">
-        <v>4.743950322028781</v>
+        <v>4.744581124684801</v>
       </c>
       <c r="K21" t="n">
-        <v>18.44058928038067</v>
+        <v>17.64223204728716</v>
       </c>
       <c r="L21" t="n">
-        <v>45.32745757604787</v>
+        <v>45.30912035273587</v>
       </c>
       <c r="M21" t="n">
-        <v>99.95287356734036</v>
+        <v>99.948924429058</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_68_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_68_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.82091205479438</v>
+        <v>45.71271393577629</v>
       </c>
       <c r="M2" t="n">
-        <v>98.92042116581862</v>
+        <v>98.55027104154431</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>87.9649233419768</v>
+        <v>88.0767444054905</v>
       </c>
       <c r="C3" t="n">
-        <v>45.89465883410496</v>
+        <v>45.9331800232965</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228596300253429</v>
+        <v>2.228853956560455</v>
       </c>
       <c r="E3" t="n">
-        <v>5.683521350615565</v>
+        <v>5.711687745094883</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7428654334178099</v>
+        <v>0.7429513188534851</v>
       </c>
       <c r="G3" t="n">
-        <v>33.96196144866307</v>
+        <v>33.97415282629453</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17180993721925</v>
+        <v>34.17576066726031</v>
       </c>
       <c r="I3" t="n">
-        <v>6.53325991294636</v>
+        <v>6.599892148592553</v>
       </c>
       <c r="J3" t="n">
-        <v>4.642908958861311</v>
+        <v>4.643445742834281</v>
       </c>
       <c r="K3" t="n">
-        <v>12.03507665802322</v>
+        <v>11.92325559450951</v>
       </c>
       <c r="L3" t="n">
-        <v>48.83573984632757</v>
+        <v>48.90667520857484</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7654753384557</v>
+        <v>106.7631108263809</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.04766316789672</v>
+        <v>87.28707783459618</v>
       </c>
       <c r="C4" t="n">
-        <v>42.60708156900124</v>
+        <v>42.78463096321357</v>
       </c>
       <c r="D4" t="n">
-        <v>2.184332405713654</v>
+        <v>2.191465448861872</v>
       </c>
       <c r="E4" t="n">
-        <v>6.479929416752189</v>
+        <v>6.534456505649357</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7444174160026867</v>
+        <v>0.744515034766017</v>
       </c>
       <c r="G4" t="n">
-        <v>33.28741636404789</v>
+        <v>33.40424429964572</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24320113612359</v>
+        <v>34.24769159923677</v>
       </c>
       <c r="I4" t="n">
-        <v>5.455757579239909</v>
+        <v>5.511485979148841</v>
       </c>
       <c r="J4" t="n">
-        <v>4.652608850016792</v>
+        <v>4.653218967287605</v>
       </c>
       <c r="K4" t="n">
-        <v>12.95233683210329</v>
+        <v>12.71292216540381</v>
       </c>
       <c r="L4" t="n">
-        <v>44.2591021568692</v>
+        <v>44.31911653392172</v>
       </c>
       <c r="M4" t="n">
-        <v>99.81852055797373</v>
+        <v>99.8166696625391</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>85.88214259982041</v>
+        <v>86.25631838976076</v>
       </c>
       <c r="C5" t="n">
-        <v>42.28831914266787</v>
+        <v>42.60940600785821</v>
       </c>
       <c r="D5" t="n">
-        <v>2.127400331374317</v>
+        <v>2.141650136760619</v>
       </c>
       <c r="E5" t="n">
-        <v>7.070121218344913</v>
+        <v>7.152763703893174</v>
       </c>
       <c r="F5" t="n">
-        <v>0.745733347425016</v>
+        <v>0.7458388283674567</v>
       </c>
       <c r="G5" t="n">
-        <v>32.41981871359631</v>
+        <v>32.64491548788755</v>
       </c>
       <c r="H5" t="n">
-        <v>34.30373398155074</v>
+        <v>34.308586104903</v>
       </c>
       <c r="I5" t="n">
-        <v>4.554501586122768</v>
+        <v>4.601071450652351</v>
       </c>
       <c r="J5" t="n">
-        <v>4.660833421406349</v>
+        <v>4.661492677296604</v>
       </c>
       <c r="K5" t="n">
-        <v>14.11785740017961</v>
+        <v>13.74368161023923</v>
       </c>
       <c r="L5" t="n">
-        <v>43.44227463550697</v>
+        <v>43.49381554914842</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84845117835444</v>
+        <v>99.84690316724587</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>84.53809649076355</v>
+        <v>85.07178804542994</v>
       </c>
       <c r="C6" t="n">
-        <v>41.651597166423</v>
+        <v>42.13967551405749</v>
       </c>
       <c r="D6" t="n">
-        <v>2.061780736666761</v>
+        <v>2.084292914277061</v>
       </c>
       <c r="E6" t="n">
-        <v>7.485561301124349</v>
+        <v>7.601199098071024</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7468510335985747</v>
+        <v>0.746961024731978</v>
       </c>
       <c r="G6" t="n">
-        <v>31.41983044946723</v>
+        <v>31.77062624313356</v>
       </c>
       <c r="H6" t="n">
-        <v>34.35514754553444</v>
+        <v>34.36020713767098</v>
       </c>
       <c r="I6" t="n">
-        <v>3.801106464381095</v>
+        <v>3.83999522297049</v>
       </c>
       <c r="J6" t="n">
-        <v>4.667818959991092</v>
+        <v>4.668506404574861</v>
       </c>
       <c r="K6" t="n">
-        <v>15.46190350923645</v>
+        <v>14.92821195457004</v>
       </c>
       <c r="L6" t="n">
-        <v>42.75998539139272</v>
+        <v>42.80430499107656</v>
       </c>
       <c r="M6" t="n">
-        <v>99.87348606705217</v>
+        <v>99.8721924597041</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82.97279389475374</v>
+        <v>83.6939004351716</v>
       </c>
       <c r="C7" t="n">
-        <v>40.67665237823338</v>
+        <v>41.35852433981229</v>
       </c>
       <c r="D7" t="n">
-        <v>1.985529433156063</v>
+        <v>2.017588121061712</v>
       </c>
       <c r="E7" t="n">
-        <v>7.73732521760115</v>
+        <v>7.891946928312096</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7478026431991167</v>
+        <v>0.7479142294236664</v>
       </c>
       <c r="G7" t="n">
-        <v>30.25782375047642</v>
+        <v>30.75385310181843</v>
       </c>
       <c r="H7" t="n">
-        <v>34.39892158715937</v>
+        <v>34.40405455348864</v>
       </c>
       <c r="I7" t="n">
-        <v>3.171624743167141</v>
+        <v>3.204079567169128</v>
       </c>
       <c r="J7" t="n">
-        <v>4.673766519994479</v>
+        <v>4.674463933897914</v>
       </c>
       <c r="K7" t="n">
-        <v>17.02720610524625</v>
+        <v>16.30609956482839</v>
       </c>
       <c r="L7" t="n">
-        <v>42.19055522584311</v>
+        <v>42.22870956138792</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89441370932275</v>
+        <v>99.89333346602859</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87.85591888953029</v>
+        <v>88.67042553142483</v>
       </c>
       <c r="C8" t="n">
-        <v>42.96391801606865</v>
+        <v>43.73353131740992</v>
       </c>
       <c r="D8" t="n">
-        <v>1.989780953383558</v>
+        <v>2.021897312916664</v>
       </c>
       <c r="E8" t="n">
-        <v>9.560911394204687</v>
+        <v>9.775900990949085</v>
       </c>
       <c r="F8" t="n">
-        <v>0.749403877615814</v>
+        <v>0.7495116346978106</v>
       </c>
       <c r="G8" t="n">
-        <v>30.75581839562273</v>
+        <v>31.27962804345444</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47257837032745</v>
+        <v>34.47753519609928</v>
       </c>
       <c r="I8" t="n">
-        <v>5.643651663277211</v>
+        <v>5.681504636446229</v>
       </c>
       <c r="J8" t="n">
-        <v>4.683774235098837</v>
+        <v>4.684447716861316</v>
       </c>
       <c r="K8" t="n">
-        <v>12.14408111046973</v>
+        <v>11.3295744685752</v>
       </c>
       <c r="L8" t="n">
-        <v>44.70428110680653</v>
+        <v>44.74791435186556</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81228023334489</v>
+        <v>99.81102013785068</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85.77538503729259</v>
+        <v>86.97510789846052</v>
       </c>
       <c r="C9" t="n">
-        <v>41.75922127737763</v>
+        <v>42.92071821522681</v>
       </c>
       <c r="D9" t="n">
-        <v>1.895392375393954</v>
+        <v>1.945856113526063</v>
       </c>
       <c r="E9" t="n">
-        <v>9.892649341520585</v>
+        <v>10.19877307480198</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7507760397406954</v>
+        <v>0.7508741237665691</v>
       </c>
       <c r="G9" t="n">
-        <v>29.29686485687622</v>
+        <v>30.10323772050326</v>
       </c>
       <c r="H9" t="n">
-        <v>34.535697828072</v>
+        <v>34.54020969326217</v>
       </c>
       <c r="I9" t="n">
-        <v>4.711654347309809</v>
+        <v>4.743193899059435</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692350248379347</v>
+        <v>4.692963273541057</v>
       </c>
       <c r="K9" t="n">
-        <v>14.22461496270739</v>
+        <v>13.02489210153947</v>
       </c>
       <c r="L9" t="n">
-        <v>43.8593956581573</v>
+        <v>43.89657010999911</v>
       </c>
       <c r="M9" t="n">
-        <v>99.84323189824232</v>
+        <v>99.8421804267654</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>83.52587153513933</v>
+        <v>85.10645209734346</v>
       </c>
       <c r="C10" t="n">
-        <v>40.24056554850455</v>
+        <v>41.78886216190574</v>
       </c>
       <c r="D10" t="n">
-        <v>1.794426085684283</v>
+        <v>1.862673043761163</v>
       </c>
       <c r="E10" t="n">
-        <v>10.02109793905078</v>
+        <v>10.42258585167211</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7519543003346333</v>
+        <v>0.752038372818428</v>
       </c>
       <c r="G10" t="n">
-        <v>27.73624037451297</v>
+        <v>28.81635956643648</v>
       </c>
       <c r="H10" t="n">
-        <v>34.58989781539314</v>
+        <v>34.59376514964768</v>
       </c>
       <c r="I10" t="n">
-        <v>3.93254064307208</v>
+        <v>3.958790282892428</v>
       </c>
       <c r="J10" t="n">
-        <v>4.699714377091459</v>
+        <v>4.700239830115175</v>
       </c>
       <c r="K10" t="n">
-        <v>16.47412846486066</v>
+        <v>14.89354790265652</v>
       </c>
       <c r="L10" t="n">
-        <v>43.15442669920952</v>
+        <v>43.18583454935276</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86912071257473</v>
+        <v>99.86824461391502</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>81.23321525121654</v>
+        <v>83.14726675265374</v>
       </c>
       <c r="C11" t="n">
-        <v>38.55724861608654</v>
+        <v>40.44430347373351</v>
       </c>
       <c r="D11" t="n">
-        <v>1.692686658702857</v>
+        <v>1.776234415531812</v>
       </c>
       <c r="E11" t="n">
-        <v>9.99984866136159</v>
+        <v>10.4894786883557</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7529668420572246</v>
+        <v>0.7530342981401794</v>
       </c>
       <c r="G11" t="n">
-        <v>26.16366559707602</v>
+        <v>27.47911651144659</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63647473463234</v>
+        <v>34.63957771444824</v>
       </c>
       <c r="I11" t="n">
-        <v>3.281529994528857</v>
+        <v>3.303360761355081</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706042762857655</v>
+        <v>4.706464363376122</v>
       </c>
       <c r="K11" t="n">
-        <v>18.76678474878347</v>
+        <v>16.85273324734626</v>
       </c>
       <c r="L11" t="n">
-        <v>42.56672939504466</v>
+        <v>42.59299688217321</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89076275991467</v>
+        <v>99.89003360325299</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>78.93314943946869</v>
+        <v>81.12247440008488</v>
       </c>
       <c r="C12" t="n">
-        <v>36.76487000224552</v>
+        <v>38.93187166664917</v>
       </c>
       <c r="D12" t="n">
-        <v>1.591680563478078</v>
+        <v>1.687653464973528</v>
       </c>
       <c r="E12" t="n">
-        <v>9.859432112990467</v>
+        <v>10.42568721363378</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538373888497653</v>
+        <v>0.7538870419874071</v>
       </c>
       <c r="G12" t="n">
-        <v>24.60242584538287</v>
+        <v>26.10873080120406</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67651988708921</v>
+        <v>34.67880393142072</v>
       </c>
       <c r="I12" t="n">
-        <v>2.737769961367277</v>
+        <v>2.755917934444096</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711483680311034</v>
+        <v>4.711794012421294</v>
       </c>
       <c r="K12" t="n">
-        <v>21.06685056053131</v>
+        <v>18.87752559991513</v>
       </c>
       <c r="L12" t="n">
-        <v>42.07712582626404</v>
+        <v>42.09884271228693</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90884638904087</v>
+        <v>99.90823997885123</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>76.65016809022124</v>
+        <v>79.07993040468733</v>
       </c>
       <c r="C13" t="n">
-        <v>34.90464038942142</v>
+        <v>37.31618090618515</v>
       </c>
       <c r="D13" t="n">
-        <v>1.492372874309599</v>
+        <v>1.599015110250784</v>
       </c>
       <c r="E13" t="n">
-        <v>9.624908645307578</v>
+        <v>10.26125013188666</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7545860583117234</v>
+        <v>0.754617549022207</v>
       </c>
       <c r="G13" t="n">
-        <v>23.06743816336643</v>
+        <v>24.73745702364923</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71095868233929</v>
+        <v>34.71240725502151</v>
       </c>
       <c r="I13" t="n">
-        <v>2.283740802138353</v>
+        <v>2.298823653468152</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716162864448274</v>
+        <v>4.716359681388794</v>
       </c>
       <c r="K13" t="n">
-        <v>23.34983190977875</v>
+        <v>20.92006959531266</v>
       </c>
       <c r="L13" t="n">
-        <v>41.66947853520631</v>
+        <v>41.68719622254542</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92395083440647</v>
+        <v>99.92344672404323</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>83.50645203658979</v>
+        <v>85.08905878826675</v>
       </c>
       <c r="C14" t="n">
-        <v>39.25537494317864</v>
+        <v>41.03676351961549</v>
       </c>
       <c r="D14" t="n">
-        <v>1.494046454304713</v>
+        <v>1.600851152973154</v>
       </c>
       <c r="E14" t="n">
-        <v>12.0302718619275</v>
+        <v>12.36161485507842</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7554322678304849</v>
+        <v>0.7554840261744068</v>
       </c>
       <c r="G14" t="n">
-        <v>25.019646206026</v>
+        <v>26.36593327214248</v>
       </c>
       <c r="H14" t="n">
-        <v>36.67622402679568</v>
+        <v>36.35233707556727</v>
       </c>
       <c r="I14" t="n">
-        <v>2.809379545764878</v>
+        <v>2.931063242740995</v>
       </c>
       <c r="J14" t="n">
-        <v>4.721451673940533</v>
+        <v>4.721775163590043</v>
       </c>
       <c r="K14" t="n">
-        <v>16.49354796341022</v>
+        <v>14.91094121173323</v>
       </c>
       <c r="L14" t="n">
-        <v>44.15753600759773</v>
+        <v>43.95470521672713</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90645891418659</v>
+        <v>99.90240994807586</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>82.85631907188345</v>
+        <v>84.63745484431324</v>
       </c>
       <c r="C15" t="n">
-        <v>39.03022700054091</v>
+        <v>41.03574883043362</v>
       </c>
       <c r="D15" t="n">
-        <v>1.469156496829011</v>
+        <v>1.584016927032324</v>
       </c>
       <c r="E15" t="n">
-        <v>12.22965100986191</v>
+        <v>12.64273286169852</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7561444433560087</v>
+        <v>0.7562114765247989</v>
       </c>
       <c r="G15" t="n">
-        <v>24.61207037101325</v>
+        <v>26.09230060427751</v>
       </c>
       <c r="H15" t="n">
-        <v>36.72003726512371</v>
+        <v>36.39096662709052</v>
       </c>
       <c r="I15" t="n">
-        <v>2.343356714724492</v>
+        <v>2.444904619409566</v>
       </c>
       <c r="J15" t="n">
-        <v>4.725902770975057</v>
+        <v>4.726321728279993</v>
       </c>
       <c r="K15" t="n">
-        <v>17.14368092811655</v>
+        <v>15.36254515568677</v>
       </c>
       <c r="L15" t="n">
-        <v>43.74805375062687</v>
+        <v>43.52028759047015</v>
       </c>
       <c r="M15" t="n">
-        <v>99.92196167928432</v>
+        <v>99.91858157659054</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>80.46826686868832</v>
+        <v>82.52753176573117</v>
       </c>
       <c r="C16" t="n">
-        <v>37.00443632824344</v>
+        <v>39.30490887698022</v>
       </c>
       <c r="D16" t="n">
-        <v>1.378694056052954</v>
+        <v>1.502360584712068</v>
       </c>
       <c r="E16" t="n">
-        <v>11.8023471984361</v>
+        <v>12.33084758691945</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7567566069196529</v>
+        <v>0.7568342948282327</v>
       </c>
       <c r="G16" t="n">
-        <v>23.09659672125607</v>
+        <v>24.74723806504214</v>
       </c>
       <c r="H16" t="n">
-        <v>36.74976527419245</v>
+        <v>36.42093834902095</v>
       </c>
       <c r="I16" t="n">
-        <v>1.954378218583254</v>
+        <v>2.03909854253189</v>
       </c>
       <c r="J16" t="n">
-        <v>4.729728793247832</v>
+        <v>4.730214342676454</v>
       </c>
       <c r="K16" t="n">
-        <v>19.5317331313117</v>
+        <v>17.4724682342688</v>
       </c>
       <c r="L16" t="n">
-        <v>43.39873729836918</v>
+        <v>43.15470887154515</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93490675792431</v>
+        <v>99.93208598279418</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>82.27876671495211</v>
+        <v>84.16219078068735</v>
       </c>
       <c r="C17" t="n">
-        <v>38.3205109787443</v>
+        <v>40.50231953947158</v>
       </c>
       <c r="D17" t="n">
-        <v>1.379774190738968</v>
+        <v>1.503568015790813</v>
       </c>
       <c r="E17" t="n">
-        <v>12.61630849687283</v>
+        <v>13.09284604922522</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7573494861421426</v>
+        <v>0.7574425544287142</v>
       </c>
       <c r="G17" t="n">
-        <v>23.597100921146</v>
+        <v>25.18101419957375</v>
       </c>
       <c r="H17" t="n">
-        <v>37.26096601757096</v>
+        <v>36.86409651118979</v>
       </c>
       <c r="I17" t="n">
-        <v>1.933833314092815</v>
+        <v>2.029207485299602</v>
       </c>
       <c r="J17" t="n">
-        <v>4.733434288388393</v>
+        <v>4.734015965179464</v>
       </c>
       <c r="K17" t="n">
-        <v>17.7212332850479</v>
+        <v>15.83780921931265</v>
       </c>
       <c r="L17" t="n">
-        <v>43.89384508811208</v>
+        <v>43.59228530979353</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93558935190428</v>
+        <v>99.93241406857776</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>79.94300239448513</v>
+        <v>82.0872375553306</v>
       </c>
       <c r="C18" t="n">
-        <v>36.28335673472364</v>
+        <v>38.74175196662001</v>
       </c>
       <c r="D18" t="n">
-        <v>1.294915273054345</v>
+        <v>1.426115034080562</v>
       </c>
       <c r="E18" t="n">
-        <v>12.1091484354784</v>
+        <v>12.70042506857751</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7578587282869763</v>
+        <v>0.7579630251871197</v>
       </c>
       <c r="G18" t="n">
-        <v>22.14583124375712</v>
+        <v>23.88386993222954</v>
       </c>
       <c r="H18" t="n">
-        <v>37.28602030835818</v>
+        <v>36.88942738830638</v>
       </c>
       <c r="I18" t="n">
-        <v>1.612611353756506</v>
+        <v>1.692168199529983</v>
       </c>
       <c r="J18" t="n">
-        <v>4.736617051793604</v>
+        <v>4.737268907419498</v>
       </c>
       <c r="K18" t="n">
-        <v>20.05699760551487</v>
+        <v>17.91276244466941</v>
       </c>
       <c r="L18" t="n">
-        <v>43.60592806770337</v>
+        <v>43.28911871411892</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94628240794187</v>
+        <v>99.94363312540834</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>79.01590858493375</v>
+        <v>81.25285018149123</v>
       </c>
       <c r="C19" t="n">
-        <v>35.59899489313587</v>
+        <v>38.1690090472812</v>
       </c>
       <c r="D19" t="n">
-        <v>1.261625218827049</v>
+        <v>1.395616962868634</v>
       </c>
       <c r="E19" t="n">
-        <v>12.02285432323159</v>
+        <v>12.66398052482555</v>
       </c>
       <c r="F19" t="n">
-        <v>0.758290354840946</v>
+        <v>0.7584017596565676</v>
       </c>
       <c r="G19" t="n">
-        <v>21.57649984551491</v>
+        <v>23.37310330499236</v>
       </c>
       <c r="H19" t="n">
-        <v>37.30725597650615</v>
+        <v>36.91078022850522</v>
       </c>
       <c r="I19" t="n">
-        <v>1.350068148257179</v>
+        <v>1.410956402789353</v>
       </c>
       <c r="J19" t="n">
-        <v>4.739314717755915</v>
+        <v>4.740010997853548</v>
       </c>
       <c r="K19" t="n">
-        <v>20.98409141506626</v>
+        <v>18.74714981850877</v>
       </c>
       <c r="L19" t="n">
-        <v>43.37193703593831</v>
+        <v>43.03683646200086</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95502334414044</v>
+        <v>99.95299532779083</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>76.51566225409726</v>
+        <v>78.94153137886001</v>
       </c>
       <c r="C20" t="n">
-        <v>33.30653287661374</v>
+        <v>36.07574991676596</v>
       </c>
       <c r="D20" t="n">
-        <v>1.171715128490596</v>
+        <v>1.310093666466009</v>
       </c>
       <c r="E20" t="n">
-        <v>11.35364350466063</v>
+        <v>12.08399631574857</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7586621907169834</v>
+        <v>0.7587784812833792</v>
       </c>
       <c r="G20" t="n">
-        <v>20.03884427133552</v>
+        <v>21.94080139480829</v>
       </c>
       <c r="H20" t="n">
-        <v>37.32554999293404</v>
+        <v>36.92911495544581</v>
       </c>
       <c r="I20" t="n">
-        <v>1.125608473978339</v>
+        <v>1.176381057086829</v>
       </c>
       <c r="J20" t="n">
-        <v>4.741638691981148</v>
+        <v>4.742365508021121</v>
       </c>
       <c r="K20" t="n">
-        <v>23.48433774590274</v>
+        <v>21.05846862114</v>
       </c>
       <c r="L20" t="n">
-        <v>43.17162748447638</v>
+        <v>42.82658822868322</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96249810699285</v>
+        <v>99.96080676658919</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>82.35776795271285</v>
+        <v>84.02777970249892</v>
       </c>
       <c r="C21" t="n">
-        <v>36.99757202903496</v>
+        <v>39.17285852427891</v>
       </c>
       <c r="D21" t="n">
-        <v>1.172442238491463</v>
+        <v>1.310993566031668</v>
       </c>
       <c r="E21" t="n">
-        <v>13.32695083422145</v>
+        <v>13.77724475347876</v>
       </c>
       <c r="F21" t="n">
-        <v>0.759132979949568</v>
+        <v>0.7592996840364467</v>
       </c>
       <c r="G21" t="n">
-        <v>21.76200488846296</v>
+        <v>23.35222824441161</v>
       </c>
       <c r="H21" t="n">
-        <v>39.05943790742804</v>
+        <v>38.35083723445882</v>
       </c>
       <c r="I21" t="n">
-        <v>1.533217979474565</v>
+        <v>1.731553194853837</v>
       </c>
       <c r="J21" t="n">
-        <v>4.744581124684801</v>
+        <v>4.745623025227792</v>
       </c>
       <c r="K21" t="n">
-        <v>17.64223204728716</v>
+        <v>15.97222029750108</v>
       </c>
       <c r="L21" t="n">
-        <v>45.30912035273587</v>
+        <v>44.79724235780715</v>
       </c>
       <c r="M21" t="n">
-        <v>99.948924429058</v>
+        <v>99.94232117958714</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_benthic_cover_iteration_68_growth_param_0.5.xlsx
+++ b/output/yearly_benthic_cover_iteration_68_growth_param_0.5.xlsx
@@ -530,10 +530,10 @@
         <v>17.9</v>
       </c>
       <c r="L2" t="n">
-        <v>45.71271393577629</v>
+        <v>43.51886915636854</v>
       </c>
       <c r="M2" t="n">
-        <v>98.55027104154431</v>
+        <v>96.29836983857132</v>
       </c>
     </row>
     <row r="3">
@@ -541,40 +541,40 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>88.0767444054905</v>
+        <v>81.4046044278392</v>
       </c>
       <c r="C3" t="n">
-        <v>45.9331800232965</v>
+        <v>43.16015998339476</v>
       </c>
       <c r="D3" t="n">
-        <v>2.228853956560455</v>
+        <v>2.176384952835543</v>
       </c>
       <c r="E3" t="n">
-        <v>5.711687745094883</v>
+        <v>4.142267744493932</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7429513188534851</v>
+        <v>0.737581911145575</v>
       </c>
       <c r="G3" t="n">
-        <v>33.97415282629453</v>
+        <v>32.7364569989013</v>
       </c>
       <c r="H3" t="n">
-        <v>34.17576066726031</v>
+        <v>33.92876791269645</v>
       </c>
       <c r="I3" t="n">
-        <v>6.599892148592553</v>
+        <v>3.073257963106563</v>
       </c>
       <c r="J3" t="n">
-        <v>4.643445742834281</v>
+        <v>4.609886944659844</v>
       </c>
       <c r="K3" t="n">
-        <v>11.92325559450951</v>
+        <v>18.5953955721608</v>
       </c>
       <c r="L3" t="n">
-        <v>48.90667520857484</v>
+        <v>45.13333333333333</v>
       </c>
       <c r="M3" t="n">
-        <v>106.7631108263809</v>
+        <v>106.8888888888889</v>
       </c>
     </row>
     <row r="4">
@@ -582,40 +582,40 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>87.28707783459618</v>
+        <v>88.51504043507369</v>
       </c>
       <c r="C4" t="n">
-        <v>42.78463096321357</v>
+        <v>42.7190625861616</v>
       </c>
       <c r="D4" t="n">
-        <v>2.191465448861872</v>
+        <v>2.182156384492262</v>
       </c>
       <c r="E4" t="n">
-        <v>6.534456505649357</v>
+        <v>6.500553241019499</v>
       </c>
       <c r="F4" t="n">
-        <v>0.744515034766017</v>
+        <v>0.7395378627275152</v>
       </c>
       <c r="G4" t="n">
-        <v>33.40424429964572</v>
+        <v>33.41009935392398</v>
       </c>
       <c r="H4" t="n">
-        <v>34.24769159923677</v>
+        <v>34.0187416854657</v>
       </c>
       <c r="I4" t="n">
-        <v>5.511485979148841</v>
+        <v>7.04184026539777</v>
       </c>
       <c r="J4" t="n">
-        <v>4.653218967287605</v>
+        <v>4.62211164204697</v>
       </c>
       <c r="K4" t="n">
-        <v>12.71292216540381</v>
+        <v>11.48495956492633</v>
       </c>
       <c r="L4" t="n">
-        <v>44.31911653392172</v>
+        <v>45.56187065563608</v>
       </c>
       <c r="M4" t="n">
-        <v>99.8166696625391</v>
+        <v>99.765892806724</v>
       </c>
     </row>
     <row r="5">
@@ -623,40 +623,40 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>86.25631838976076</v>
+        <v>87.49196288087757</v>
       </c>
       <c r="C5" t="n">
-        <v>42.60940600785821</v>
+        <v>42.78730265816127</v>
       </c>
       <c r="D5" t="n">
-        <v>2.141650136760619</v>
+        <v>2.13388921807612</v>
       </c>
       <c r="E5" t="n">
-        <v>7.152763703893174</v>
+        <v>7.336992225811299</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7458388283674567</v>
+        <v>0.7411949598612279</v>
       </c>
       <c r="G5" t="n">
-        <v>32.64491548788755</v>
+        <v>32.67110061077436</v>
       </c>
       <c r="H5" t="n">
-        <v>34.308586104903</v>
+        <v>34.09496815361648</v>
       </c>
       <c r="I5" t="n">
-        <v>4.601071450652351</v>
+        <v>5.881349213605411</v>
       </c>
       <c r="J5" t="n">
-        <v>4.661492677296604</v>
+        <v>4.632468499132673</v>
       </c>
       <c r="K5" t="n">
-        <v>13.74368161023923</v>
+        <v>12.50803711912245</v>
       </c>
       <c r="L5" t="n">
-        <v>43.49381554914842</v>
+        <v>44.50905354867747</v>
       </c>
       <c r="M5" t="n">
-        <v>99.84690316724587</v>
+        <v>99.80439332596119</v>
       </c>
     </row>
     <row r="6">
@@ -664,40 +664,40 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>85.07178804542994</v>
+        <v>86.19530460233656</v>
       </c>
       <c r="C6" t="n">
-        <v>42.13967551405749</v>
+        <v>42.40337279342724</v>
       </c>
       <c r="D6" t="n">
-        <v>2.084292914277061</v>
+        <v>2.072159484892608</v>
       </c>
       <c r="E6" t="n">
-        <v>7.601199098071024</v>
+        <v>7.943150927178137</v>
       </c>
       <c r="F6" t="n">
-        <v>0.746961024731978</v>
+        <v>0.7426024560865071</v>
       </c>
       <c r="G6" t="n">
-        <v>31.77062624313356</v>
+        <v>31.72598204209203</v>
       </c>
       <c r="H6" t="n">
-        <v>34.36020713767098</v>
+        <v>34.15971297997933</v>
       </c>
       <c r="I6" t="n">
-        <v>3.83999522297049</v>
+        <v>4.910431361567298</v>
       </c>
       <c r="J6" t="n">
-        <v>4.668506404574861</v>
+        <v>4.641265350540668</v>
       </c>
       <c r="K6" t="n">
-        <v>14.92821195457004</v>
+        <v>13.80469539766342</v>
       </c>
       <c r="L6" t="n">
-        <v>42.80430499107656</v>
+        <v>43.62856099742032</v>
       </c>
       <c r="M6" t="n">
-        <v>99.8721924597041</v>
+        <v>99.83662918851098</v>
       </c>
     </row>
     <row r="7">
@@ -705,40 +705,40 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>83.6939004351716</v>
+        <v>84.7727199846683</v>
       </c>
       <c r="C7" t="n">
-        <v>41.35852433981229</v>
+        <v>41.74331464835424</v>
       </c>
       <c r="D7" t="n">
-        <v>2.017588121061712</v>
+        <v>2.004763938058227</v>
       </c>
       <c r="E7" t="n">
-        <v>7.891946928312096</v>
+        <v>8.367908946645722</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7479142294236664</v>
+        <v>0.7437992427969018</v>
       </c>
       <c r="G7" t="n">
-        <v>30.75385310181843</v>
+        <v>30.69411652972518</v>
       </c>
       <c r="H7" t="n">
-        <v>34.40405455348864</v>
+        <v>34.21476516865748</v>
       </c>
       <c r="I7" t="n">
-        <v>3.204079567169128</v>
+        <v>4.098620891304149</v>
       </c>
       <c r="J7" t="n">
-        <v>4.674463933897914</v>
+        <v>4.648745267480635</v>
       </c>
       <c r="K7" t="n">
-        <v>16.30609956482839</v>
+        <v>15.22728001533169</v>
       </c>
       <c r="L7" t="n">
-        <v>42.22870956138792</v>
+        <v>42.89300446515941</v>
       </c>
       <c r="M7" t="n">
-        <v>99.89333346602859</v>
+        <v>99.86359912884535</v>
       </c>
     </row>
     <row r="8">
@@ -746,40 +746,40 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>88.67042553142483</v>
+        <v>83.05911760584416</v>
       </c>
       <c r="C8" t="n">
-        <v>43.73353131740992</v>
+        <v>40.66623917997191</v>
       </c>
       <c r="D8" t="n">
-        <v>2.021897312916664</v>
+        <v>1.923747654815161</v>
       </c>
       <c r="E8" t="n">
-        <v>9.775900990949085</v>
+        <v>8.599780257088547</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7495116346978106</v>
+        <v>0.7448201808017609</v>
       </c>
       <c r="G8" t="n">
-        <v>31.27962804345444</v>
+        <v>29.4537095214684</v>
       </c>
       <c r="H8" t="n">
-        <v>34.47753519609928</v>
+        <v>34.261728316881</v>
       </c>
       <c r="I8" t="n">
-        <v>5.681504636446229</v>
+        <v>3.420205544778293</v>
       </c>
       <c r="J8" t="n">
-        <v>4.684447716861316</v>
+        <v>4.655126130011005</v>
       </c>
       <c r="K8" t="n">
-        <v>11.3295744685752</v>
+        <v>16.94088239415584</v>
       </c>
       <c r="L8" t="n">
-        <v>44.74791435186556</v>
+        <v>42.27902784555824</v>
       </c>
       <c r="M8" t="n">
-        <v>99.81102013785068</v>
+        <v>99.88614941968598</v>
       </c>
     </row>
     <row r="9">
@@ -787,40 +787,40 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>86.97510789846052</v>
+        <v>81.32160947303096</v>
       </c>
       <c r="C9" t="n">
-        <v>42.92071821522681</v>
+        <v>39.45957802924653</v>
       </c>
       <c r="D9" t="n">
-        <v>1.945856113526063</v>
+        <v>1.842289188782621</v>
       </c>
       <c r="E9" t="n">
-        <v>10.19877307480198</v>
+        <v>8.711218471207651</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7508741237665691</v>
+        <v>0.7456913506710632</v>
       </c>
       <c r="G9" t="n">
-        <v>30.10323772050326</v>
+        <v>28.20653243429615</v>
       </c>
       <c r="H9" t="n">
-        <v>34.54020969326217</v>
+        <v>34.3018021308689</v>
       </c>
       <c r="I9" t="n">
-        <v>4.743193899059435</v>
+        <v>2.853504955510413</v>
       </c>
       <c r="J9" t="n">
-        <v>4.692963273541057</v>
+        <v>4.660570941694143</v>
       </c>
       <c r="K9" t="n">
-        <v>13.02489210153947</v>
+        <v>18.67839052696905</v>
       </c>
       <c r="L9" t="n">
-        <v>43.89657010999911</v>
+        <v>41.76702573420724</v>
       </c>
       <c r="M9" t="n">
-        <v>99.8421804267654</v>
+        <v>99.90499429042282</v>
       </c>
     </row>
     <row r="10">
@@ -828,40 +828,40 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>85.10645209734346</v>
+        <v>85.92649939746633</v>
       </c>
       <c r="C10" t="n">
-        <v>41.78886216190574</v>
+        <v>42.66032539346752</v>
       </c>
       <c r="D10" t="n">
-        <v>1.862673043761163</v>
+        <v>1.844342599150476</v>
       </c>
       <c r="E10" t="n">
-        <v>10.42258585167211</v>
+        <v>10.53941658462172</v>
       </c>
       <c r="F10" t="n">
-        <v>0.752038372818428</v>
+        <v>0.7465224961611472</v>
       </c>
       <c r="G10" t="n">
-        <v>28.81635956643648</v>
+        <v>29.57759279268655</v>
       </c>
       <c r="H10" t="n">
-        <v>34.59376514964768</v>
+        <v>35.67965625978458</v>
       </c>
       <c r="I10" t="n">
-        <v>3.958790282892428</v>
+        <v>2.873203064054695</v>
       </c>
       <c r="J10" t="n">
-        <v>4.700239830115175</v>
+        <v>4.665765601007168</v>
       </c>
       <c r="K10" t="n">
-        <v>14.89354790265652</v>
+        <v>14.07350060253366</v>
       </c>
       <c r="L10" t="n">
-        <v>43.18583454935276</v>
+        <v>43.1705071984837</v>
       </c>
       <c r="M10" t="n">
-        <v>99.86824461391502</v>
+        <v>99.90433319448488</v>
       </c>
     </row>
     <row r="11">
@@ -869,40 +869,40 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>83.14726675265374</v>
+        <v>85.68016908099376</v>
       </c>
       <c r="C11" t="n">
-        <v>40.44430347373351</v>
+        <v>42.76818277171137</v>
       </c>
       <c r="D11" t="n">
-        <v>1.776234415531812</v>
+        <v>1.828942321962947</v>
       </c>
       <c r="E11" t="n">
-        <v>10.4894786883557</v>
+        <v>10.88249175534576</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7530342981401794</v>
+        <v>0.747238947043503</v>
       </c>
       <c r="G11" t="n">
-        <v>27.47911651144659</v>
+        <v>29.35055513104299</v>
       </c>
       <c r="H11" t="n">
-        <v>34.63957771444824</v>
+        <v>35.73383416136748</v>
       </c>
       <c r="I11" t="n">
-        <v>3.303360761355081</v>
+        <v>2.4668633452092</v>
       </c>
       <c r="J11" t="n">
-        <v>4.706464363376122</v>
+        <v>4.670243419021892</v>
       </c>
       <c r="K11" t="n">
-        <v>16.85273324734626</v>
+        <v>14.31983091900623</v>
       </c>
       <c r="L11" t="n">
-        <v>42.59299688217321</v>
+        <v>42.82983637186098</v>
       </c>
       <c r="M11" t="n">
-        <v>99.89003360325299</v>
+        <v>99.91785006257858</v>
       </c>
     </row>
     <row r="12">
@@ -910,40 +910,40 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>81.12247440008488</v>
+        <v>83.84948450193063</v>
       </c>
       <c r="C12" t="n">
-        <v>38.93187166664917</v>
+        <v>41.32116348538892</v>
       </c>
       <c r="D12" t="n">
-        <v>1.687653464973528</v>
+        <v>1.750771144326018</v>
       </c>
       <c r="E12" t="n">
-        <v>10.42568721363378</v>
+        <v>10.76026120572021</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7538870419874071</v>
+        <v>0.7478501096238561</v>
       </c>
       <c r="G12" t="n">
-        <v>26.10873080120406</v>
+        <v>28.09607737559974</v>
       </c>
       <c r="H12" t="n">
-        <v>34.67880393142072</v>
+        <v>35.76306066565822</v>
       </c>
       <c r="I12" t="n">
-        <v>2.755917934444096</v>
+        <v>2.057400815853497</v>
       </c>
       <c r="J12" t="n">
-        <v>4.711794012421294</v>
+        <v>4.674063185149099</v>
       </c>
       <c r="K12" t="n">
-        <v>18.87752559991513</v>
+        <v>16.15051549806935</v>
       </c>
       <c r="L12" t="n">
-        <v>42.09884271228693</v>
+        <v>42.45979703473038</v>
       </c>
       <c r="M12" t="n">
-        <v>99.90823997885123</v>
+        <v>99.93147601818865</v>
       </c>
     </row>
     <row r="13">
@@ -951,40 +951,40 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>79.07993040468733</v>
+        <v>84.95836853387743</v>
       </c>
       <c r="C13" t="n">
-        <v>37.31618090618515</v>
+        <v>42.26662183388689</v>
       </c>
       <c r="D13" t="n">
-        <v>1.599015110250784</v>
+        <v>1.75207275776553</v>
       </c>
       <c r="E13" t="n">
-        <v>10.26125013188666</v>
+        <v>11.3823368926927</v>
       </c>
       <c r="F13" t="n">
-        <v>0.754617549022207</v>
+        <v>0.7484060999122394</v>
       </c>
       <c r="G13" t="n">
-        <v>24.73745702364923</v>
+        <v>28.41522926706617</v>
       </c>
       <c r="H13" t="n">
-        <v>34.71240725502151</v>
+        <v>36.08791258737885</v>
       </c>
       <c r="I13" t="n">
-        <v>2.298823653468152</v>
+        <v>1.89487280461045</v>
       </c>
       <c r="J13" t="n">
-        <v>4.716359681388794</v>
+        <v>4.677538124451495</v>
       </c>
       <c r="K13" t="n">
-        <v>20.92006959531266</v>
+        <v>15.04163146612257</v>
       </c>
       <c r="L13" t="n">
-        <v>41.68719622254542</v>
+        <v>42.62863119648615</v>
       </c>
       <c r="M13" t="n">
-        <v>99.92344672404323</v>
+        <v>99.93688449649561</v>
       </c>
     </row>
     <row r="14">
@@ -992,40 +992,40 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>85.08905878826675</v>
+        <v>83.13302466232543</v>
       </c>
       <c r="C14" t="n">
-        <v>41.03676351961549</v>
+        <v>40.73587792430275</v>
       </c>
       <c r="D14" t="n">
-        <v>1.600851152973154</v>
+        <v>1.676162580125312</v>
       </c>
       <c r="E14" t="n">
-        <v>12.36161485507842</v>
+        <v>11.15253010069751</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7554840261744068</v>
+        <v>0.748880250570336</v>
       </c>
       <c r="G14" t="n">
-        <v>26.36593327214248</v>
+        <v>27.18411309806562</v>
       </c>
       <c r="H14" t="n">
-        <v>36.35233707556727</v>
+        <v>36.11077598668125</v>
       </c>
       <c r="I14" t="n">
-        <v>2.931063242740995</v>
+        <v>1.580061080120794</v>
       </c>
       <c r="J14" t="n">
-        <v>4.721775163590043</v>
+        <v>4.680501566064599</v>
       </c>
       <c r="K14" t="n">
-        <v>14.91094121173323</v>
+        <v>16.86697533767458</v>
       </c>
       <c r="L14" t="n">
-        <v>43.95470521672713</v>
+        <v>42.34451138233906</v>
       </c>
       <c r="M14" t="n">
-        <v>99.90240994807586</v>
+        <v>99.94736464431639</v>
       </c>
     </row>
     <row r="15">
@@ -1033,40 +1033,40 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>84.63745484431324</v>
+        <v>82.3055880622321</v>
       </c>
       <c r="C15" t="n">
-        <v>41.03574883043362</v>
+        <v>40.12922820501625</v>
       </c>
       <c r="D15" t="n">
-        <v>1.584016927032324</v>
+        <v>1.641201056717499</v>
       </c>
       <c r="E15" t="n">
-        <v>12.64273286169852</v>
+        <v>11.1434315125061</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7562114765247989</v>
+        <v>0.7492870054443579</v>
       </c>
       <c r="G15" t="n">
-        <v>26.09230060427751</v>
+        <v>26.61710485097328</v>
       </c>
       <c r="H15" t="n">
-        <v>36.39096662709052</v>
+        <v>36.13038958194712</v>
       </c>
       <c r="I15" t="n">
-        <v>2.444904619409566</v>
+        <v>1.341130270616514</v>
       </c>
       <c r="J15" t="n">
-        <v>4.726321728279993</v>
+        <v>4.683043784027236</v>
       </c>
       <c r="K15" t="n">
-        <v>15.36254515568677</v>
+        <v>17.69441193776788</v>
       </c>
       <c r="L15" t="n">
-        <v>43.52028759047015</v>
+        <v>42.13167978287813</v>
       </c>
       <c r="M15" t="n">
-        <v>99.91858157659054</v>
+        <v>99.95531992566227</v>
       </c>
     </row>
     <row r="16">
@@ -1074,40 +1074,40 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>82.52753176573117</v>
+        <v>80.13471808617045</v>
       </c>
       <c r="C16" t="n">
-        <v>39.30490887698022</v>
+        <v>38.16642254272075</v>
       </c>
       <c r="D16" t="n">
-        <v>1.502360584712068</v>
+        <v>1.551499055041287</v>
       </c>
       <c r="E16" t="n">
-        <v>12.33084758691945</v>
+        <v>10.72072733843073</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7568342948282327</v>
+        <v>0.7496355015238466</v>
       </c>
       <c r="G16" t="n">
-        <v>24.74723806504214</v>
+        <v>25.16231198803588</v>
       </c>
       <c r="H16" t="n">
-        <v>36.42093834902095</v>
+        <v>36.14719395600969</v>
       </c>
       <c r="I16" t="n">
-        <v>2.03909854253189</v>
+        <v>1.118128362604976</v>
       </c>
       <c r="J16" t="n">
-        <v>4.730214342676454</v>
+        <v>4.68522188452404</v>
       </c>
       <c r="K16" t="n">
-        <v>17.4724682342688</v>
+        <v>19.86528191382955</v>
       </c>
       <c r="L16" t="n">
-        <v>43.15470887154515</v>
+        <v>41.93104192482145</v>
       </c>
       <c r="M16" t="n">
-        <v>99.93208598279418</v>
+        <v>99.96274638137174</v>
       </c>
     </row>
     <row r="17">
@@ -1115,40 +1115,40 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>84.16219078068735</v>
+        <v>84.61979320311384</v>
       </c>
       <c r="C17" t="n">
-        <v>40.50231953947158</v>
+        <v>41.14870781972787</v>
       </c>
       <c r="D17" t="n">
-        <v>1.503568015790813</v>
+        <v>1.552243361935152</v>
       </c>
       <c r="E17" t="n">
-        <v>13.09284604922522</v>
+        <v>12.31033598439283</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7574425544287142</v>
+        <v>0.7499951271838543</v>
       </c>
       <c r="G17" t="n">
-        <v>25.18101419957375</v>
+        <v>26.55587378163838</v>
       </c>
       <c r="H17" t="n">
-        <v>36.86409651118979</v>
+        <v>37.54602557130529</v>
       </c>
       <c r="I17" t="n">
-        <v>2.029207485299602</v>
+        <v>1.217849831759232</v>
       </c>
       <c r="J17" t="n">
-        <v>4.734015965179464</v>
+        <v>4.687469544899088</v>
       </c>
       <c r="K17" t="n">
-        <v>15.83780921931265</v>
+        <v>15.38020679688617</v>
       </c>
       <c r="L17" t="n">
-        <v>43.59228530979353</v>
+        <v>43.43050985445599</v>
       </c>
       <c r="M17" t="n">
-        <v>99.93241406857776</v>
+        <v>99.95942447107004</v>
       </c>
     </row>
     <row r="18">
@@ -1156,40 +1156,40 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>82.0872375553306</v>
+        <v>86.2810870332862</v>
       </c>
       <c r="C18" t="n">
-        <v>38.74175196662001</v>
+        <v>41.89171783120938</v>
       </c>
       <c r="D18" t="n">
-        <v>1.426115034080562</v>
+        <v>1.553495511171729</v>
       </c>
       <c r="E18" t="n">
-        <v>12.70042506857751</v>
+        <v>12.91883575720574</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7579630251871197</v>
+        <v>0.7506001262767602</v>
       </c>
       <c r="G18" t="n">
-        <v>23.88386993222954</v>
+        <v>26.70257925782763</v>
       </c>
       <c r="H18" t="n">
-        <v>36.88942738830638</v>
+        <v>37.57631284996823</v>
       </c>
       <c r="I18" t="n">
-        <v>1.692168199529983</v>
+        <v>2.088012741606357</v>
       </c>
       <c r="J18" t="n">
-        <v>4.737268907419498</v>
+        <v>4.69125078922975</v>
       </c>
       <c r="K18" t="n">
-        <v>17.91276244466941</v>
+        <v>13.7189129667138</v>
       </c>
       <c r="L18" t="n">
-        <v>43.28911871411892</v>
+        <v>44.3198248767261</v>
       </c>
       <c r="M18" t="n">
-        <v>99.94363312540834</v>
+        <v>99.93045567464928</v>
       </c>
     </row>
     <row r="19">
@@ -1197,40 +1197,40 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>81.25285018149123</v>
+        <v>83.76497565954909</v>
       </c>
       <c r="C19" t="n">
-        <v>38.1690090472812</v>
+        <v>39.6994010484123</v>
       </c>
       <c r="D19" t="n">
-        <v>1.395616962868634</v>
+        <v>1.45957533416884</v>
       </c>
       <c r="E19" t="n">
-        <v>12.66398052482555</v>
+        <v>12.42800026629253</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7584017596565676</v>
+        <v>0.7511202152278619</v>
       </c>
       <c r="G19" t="n">
-        <v>23.37310330499236</v>
+        <v>25.08821284846655</v>
       </c>
       <c r="H19" t="n">
-        <v>36.91078022850522</v>
+        <v>37.60234938320644</v>
       </c>
       <c r="I19" t="n">
-        <v>1.410956402789353</v>
+        <v>1.74121626701273</v>
       </c>
       <c r="J19" t="n">
-        <v>4.740010997853548</v>
+        <v>4.694501345174135</v>
       </c>
       <c r="K19" t="n">
-        <v>18.74714981850877</v>
+        <v>16.23502434045091</v>
       </c>
       <c r="L19" t="n">
-        <v>43.03683646200086</v>
+        <v>44.00757425720328</v>
       </c>
       <c r="M19" t="n">
-        <v>99.95299532779083</v>
+        <v>99.94199964606648</v>
       </c>
     </row>
     <row r="20">
@@ -1238,40 +1238,40 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>78.94153137886001</v>
+        <v>81.17372131652897</v>
       </c>
       <c r="C20" t="n">
-        <v>36.07574991676596</v>
+        <v>37.37748991377628</v>
       </c>
       <c r="D20" t="n">
-        <v>1.310093666466009</v>
+        <v>1.363349723986855</v>
       </c>
       <c r="E20" t="n">
-        <v>12.08399631574857</v>
+        <v>11.85063767495773</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7587784812833792</v>
+        <v>0.7515680347885648</v>
       </c>
       <c r="G20" t="n">
-        <v>21.94080139480829</v>
+        <v>23.43421902354765</v>
       </c>
       <c r="H20" t="n">
-        <v>36.92911495544581</v>
+        <v>37.62476798843208</v>
       </c>
       <c r="I20" t="n">
-        <v>1.176381057086829</v>
+        <v>1.451878653387555</v>
       </c>
       <c r="J20" t="n">
-        <v>4.742365508021121</v>
+        <v>4.697300217428529</v>
       </c>
       <c r="K20" t="n">
-        <v>21.05846862114</v>
+        <v>18.82627868347107</v>
       </c>
       <c r="L20" t="n">
-        <v>42.82658822868322</v>
+        <v>43.74786428422452</v>
       </c>
       <c r="M20" t="n">
-        <v>99.96080676658919</v>
+        <v>99.95163288147185</v>
       </c>
     </row>
     <row r="21">
@@ -1279,40 +1279,40 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>84.02777970249892</v>
+        <v>78.48834682110261</v>
       </c>
       <c r="C21" t="n">
-        <v>39.17285852427891</v>
+        <v>34.91604977482498</v>
       </c>
       <c r="D21" t="n">
-        <v>1.310993566031668</v>
+        <v>1.26410065986598</v>
       </c>
       <c r="E21" t="n">
-        <v>13.77724475347876</v>
+        <v>11.18968903473202</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7592996840364467</v>
+        <v>0.7519544143548524</v>
       </c>
       <c r="G21" t="n">
-        <v>23.35222824441161</v>
+        <v>21.72825593456906</v>
       </c>
       <c r="H21" t="n">
-        <v>38.35083723445882</v>
+        <v>37.64411080353881</v>
       </c>
       <c r="I21" t="n">
-        <v>1.731553194853837</v>
+        <v>1.210520884324073</v>
       </c>
       <c r="J21" t="n">
-        <v>4.745623025227792</v>
+        <v>4.699715089717826</v>
       </c>
       <c r="K21" t="n">
-        <v>15.97222029750108</v>
+        <v>21.51165317889737</v>
       </c>
       <c r="L21" t="n">
-        <v>44.79724235780715</v>
+        <v>43.53196708368357</v>
       </c>
       <c r="M21" t="n">
-        <v>99.94232117958714</v>
+        <v>99.95967003740591</v>
       </c>
     </row>
   </sheetData>
